--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487550_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487550_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3349</v>
+        <v>2.3326</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1697</v>
+        <v>0.0605</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1652</v>
+        <v>2.2721</v>
       </c>
       <c r="G2" t="n">
         <v>1.5847</v>
@@ -610,13 +610,13 @@
         <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1211</v>
+        <v>0.1188</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5762</v>
+        <v>0.467</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4551</v>
+        <v>-0.3482</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0881</v>
+        <v>1.488</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4664</v>
+        <v>2.0421</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5545</v>
+        <v>-0.5541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6821</v>
+        <v>2.9579</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9605</v>
+        <v>4.6394</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.2784</v>
+        <v>-1.6815</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1936</v>
+        <v>3.9924</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4772</v>
+        <v>3.952</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2836</v>
+        <v>0.0404</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5115</v>
+        <v>-1.0345</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4833</v>
+        <v>0.6874</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9948</v>
+        <v>-1.7219</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5253</v>
+        <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2862</v>
+        <v>-0.1761</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5299</v>
+        <v>-0.19</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8161</v>
+        <v>0.0138</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4469</v>
+        <v>-2.273</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.1716</v>
+        <v>-0.7811</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0471</v>
+        <v>1.2677</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7616</v>
+        <v>-0.393</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7145</v>
+        <v>1.6607</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9579</v>
+        <v>0.7825</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6394</v>
+        <v>-0.6672</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6815</v>
+        <v>1.4498</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9924</v>
+        <v>0.5763</v>
       </c>
       <c r="K4" t="n">
-        <v>3.952</v>
+        <v>-0.6006</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0404</v>
+        <v>1.1769</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0345</v>
+        <v>0.2062</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6874</v>
+        <v>-0.0667</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7219</v>
+        <v>0.2729</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6171</v>
+        <v>0.0935</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4705</v>
+        <v>0.01</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1466</v>
+        <v>0.0835</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.273</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7811</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9607</v>
+        <v>0.7655</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7</v>
+        <v>-1.0406</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6607</v>
+        <v>1.8061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7825</v>
+        <v>0.6821</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6672</v>
+        <v>3.9605</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4498</v>
+        <v>-3.2784</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5763</v>
+        <v>2.1936</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6006</v>
+        <v>3.4772</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1769</v>
+        <v>-1.2836</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2062</v>
+        <v>-1.5115</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0667</v>
+        <v>0.4833</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2729</v>
+        <v>-1.9948</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3709</v>
+        <v>3.5253</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2135</v>
+        <v>-0.0365</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.297</v>
+        <v>-0.1041</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0835</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.4469</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.1716</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.043</v>
+        <v>0.356</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7488</v>
+        <v>-1.3824</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7918</v>
+        <v>1.7384</v>
       </c>
       <c r="G6" t="n">
         <v>0.39</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3262</v>
+        <v>-0.0132</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4752</v>
+        <v>-0.1088</v>
       </c>
       <c r="U6" t="n">
-        <v>0.149</v>
+        <v>0.0956</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6083</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8532</v>
+        <v>-0.2997</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2549</v>
+        <v>-0.8885</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4017</v>
+        <v>0.5888</v>
       </c>
       <c r="G7" t="n">
         <v>0.7695</v>
@@ -1000,13 +1000,13 @@
         <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9557</v>
+        <v>-0.4021</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.594</v>
+        <v>-0.2276</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3616</v>
+        <v>-0.1745</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0441</v>
+        <v>-1.8848</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3857</v>
+        <v>-2.5739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3416</v>
+        <v>0.6891</v>
       </c>
       <c r="G8" t="n">
         <v>-4.1973</v>
@@ -1078,13 +1078,13 @@
         <v>2.7419</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2259</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3899</v>
+        <v>0.2017</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6158</v>
+        <v>-0.2683</v>
       </c>
       <c r="V8" t="n">
         <v>4.5335</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0555</v>
+        <v>-2.1309</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6005</v>
+        <v>-3.7293</v>
       </c>
       <c r="F9" t="n">
-        <v>1.545</v>
+        <v>1.5984</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5188</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.522</v>
+        <v>0.4467</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0465</v>
+        <v>-0.0823</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4756</v>
+        <v>0.529</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1899</v>
+        <v>-6.6723</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.5007</v>
+        <v>-6.9296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3108</v>
+        <v>0.2573</v>
       </c>
       <c r="G10" t="n">
         <v>-3.675</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0437</v>
+        <v>-0.5261</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0516</v>
+        <v>-0.4805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0456</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6689</v>
+        <v>-4.777900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.7257</v>
+        <v>-14.8347</v>
       </c>
       <c r="F11" t="n">
         <v>10.0568</v>
@@ -1312,13 +1312,13 @@
         <v>18.6056</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4528</v>
+        <v>-0.5616</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4056</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04699999999999994</v>
+        <v>-0.04709999999999995</v>
       </c>
       <c r="V11" t="n">
         <v>-0.01259999999999994</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4939</v>
+        <v>6.2471</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5929</v>
+        <v>2.2069</v>
       </c>
       <c r="F12" t="n">
-        <v>3.901</v>
+        <v>4.0402</v>
       </c>
       <c r="G12" t="n">
         <v>6.7673</v>
@@ -1390,13 +1390,13 @@
         <v>3.5253</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4567</v>
+        <v>0.2966</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8269</v>
+        <v>-0.2129</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3702</v>
+        <v>0.5095</v>
       </c>
       <c r="V12" t="n">
         <v>2.7086</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6299</v>
+        <v>3.6566</v>
       </c>
       <c r="E13" t="n">
         <v>-0.1584</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7882</v>
+        <v>3.815</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6716</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8718</v>
+        <v>0.8985</v>
       </c>
       <c r="T13" t="n">
         <v>0.3129</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5589</v>
+        <v>0.5856</v>
       </c>
       <c r="V13" t="n">
         <v>0.8837</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6637</v>
+        <v>2.5245</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0251</v>
+        <v>0.6158</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6386</v>
+        <v>1.9087</v>
       </c>
       <c r="G14" t="n">
         <v>0.7652</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2961</v>
+        <v>0.1569</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6099</v>
+        <v>0.2005</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3138</v>
+        <v>-0.0437</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1602</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9598</v>
+        <v>2.3259</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1483</v>
+        <v>0.1587</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1081</v>
+        <v>2.1672</v>
       </c>
       <c r="G15" t="n">
         <v>2.8224</v>
@@ -1624,13 +1624,13 @@
         <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1955</v>
+        <v>0.1706</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4288</v>
+        <v>-0.1218</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2333</v>
+        <v>0.2923</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2754</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7017</v>
+        <v>2.1854</v>
       </c>
       <c r="E16" t="n">
-        <v>0.922</v>
+        <v>-0.2146</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7796999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1647</v>
+        <v>1.9251</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4784</v>
+        <v>0.2933</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3137</v>
+        <v>1.6318</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3585</v>
+        <v>1.5762</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0003</v>
+        <v>0.3589</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6418</v>
+        <v>1.2173</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1938</v>
+        <v>0.3489</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4781</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6719000000000001</v>
+        <v>0.4145</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1751</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3618</v>
+        <v>0.1244</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5634</v>
+        <v>-0.1076</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2016</v>
+        <v>0.232</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7235</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.4481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5088</v>
+        <v>1.5016</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6239</v>
+        <v>0.6149</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1327</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9251</v>
+        <v>0.1647</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2933</v>
+        <v>1.4784</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6318</v>
+        <v>-1.3137</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5762</v>
+        <v>0.3585</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3589</v>
+        <v>1.0003</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2173</v>
+        <v>-0.6418</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3489</v>
+        <v>-0.1938</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.4781</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4145</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5523</v>
+        <v>0.1617</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.517</v>
+        <v>0.2564</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0353</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7235</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8114</v>
+        <v>-0.5367</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1325</v>
+        <v>-1.2348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3211</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-1.608</v>
@@ -1858,13 +1858,13 @@
         <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0351</v>
+        <v>0.3098</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0723</v>
+        <v>-0.1747</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1075</v>
+        <v>0.4845</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2178</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1709</v>
+        <v>-1.6918</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7583</v>
+        <v>-3.0653</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5874</v>
+        <v>1.3735</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6203</v>
@@ -1936,13 +1936,13 @@
         <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3503</v>
+        <v>-0.1706</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0882</v>
+        <v>-0.2188</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2621</v>
+        <v>0.0482</v>
       </c>
       <c r="V19" t="n">
         <v>0.6659</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5224</v>
+        <v>-4.302</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.4907</v>
+        <v>-2.907</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9683</v>
+        <v>-1.3951</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7834</v>
+        <v>-4.5371</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.9202</v>
+        <v>-4.6932</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1368</v>
+        <v>0.1561</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5948</v>
+        <v>-3.9361</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4483</v>
+        <v>-3.2683</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8535</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1886</v>
+        <v>-0.601</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4718</v>
+        <v>-1.4249</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2833</v>
+        <v>0.8239</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.917</v>
+        <v>-0.1958</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1336</v>
+        <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4188</v>
+        <v>-0.1947</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6869</v>
+        <v>-0.267</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7319</v>
+        <v>0.0723</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.3745</v>
+        <v>-0.9412</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6659</v>
+        <v>1.492</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7086</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7842</v>
+        <v>-4.8773</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0093</v>
+        <v>-5.7977</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7749</v>
+        <v>0.9205</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5371</v>
+        <v>-1.7834</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.6932</v>
+        <v>-2.9202</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1561</v>
+        <v>1.1368</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.9361</v>
+        <v>-1.5948</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.2683</v>
+        <v>-2.4483</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6677999999999999</v>
+        <v>0.8535</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.601</v>
+        <v>-0.1886</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4249</v>
+        <v>-0.4718</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8239</v>
+        <v>0.2833</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1958</v>
+        <v>-3.917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5668</v>
+        <v>3.1336</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6768</v>
+        <v>1.0639</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3694</v>
+        <v>0.3799</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3075</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9412</v>
+        <v>-3.3745</v>
       </c>
       <c r="W21" t="n">
-        <v>1.492</v>
+        <v>-0.6659</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4332</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.668899999999999</v>
+        <v>7.033300000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.781400000000001</v>
+        <v>-9.781499999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>15.4502</v>
+        <v>16.8147</v>
       </c>
       <c r="G22" t="n">
         <v>3.224299999999999</v>
@@ -2143,7 +2143,7 @@
         <v>13.4371</v>
       </c>
       <c r="J22" t="n">
-        <v>4.141</v>
+        <v>4.140999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>-3.1039</v>
@@ -2152,7 +2152,7 @@
         <v>7.245000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9169</v>
+        <v>-0.9168999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>-7.1088</v>
@@ -2170,16 +2170,16 @@
         <v>19.5848</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4526</v>
+        <v>2.8171</v>
       </c>
       <c r="T22" t="n">
-        <v>0.04689999999999989</v>
+        <v>0.04690000000000005</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4057</v>
+        <v>2.77</v>
       </c>
       <c r="V22" t="n">
-        <v>0.01260000000000061</v>
+        <v>0.01260000000000039</v>
       </c>
       <c r="W22" t="n">
         <v>4.6362</v>
